--- a/InputData/indst/CPPL/Cement Pathway Campaign Length.xlsx
+++ b/InputData/indst/CPPL/Cement Pathway Campaign Length.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -462,7 +462,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Kiln overhaul-decision recurrence interval anchor</t>
+          <t>Kiln overhaul-decision recurrence interval anchor (mean of the distributed recurrence)</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>35/35/35/30 years, identical to CPAL. Used for two purposes: the recurrence interval between overhaul decisions (feeds CPRS-style cohort turnover) and the amortization horizon for overhaul capital (CRCC).</t>
+          <t>25 years, uniform across pathways. Used for two purposes: the MEAN of the distributed (third-order delay) overhaul-decision recurrence for both the preexisting and model-run capacity pools (Q4 decision-curve change, 2026-08-26) and the amortization horizon for overhaul capital (CRCC). ECRA-INFORMED BUT UNCONFIRMED: ECRA reports most original kiln equipment is replaced after 20-30 years (snippet-tier source; the full ECRA Technology Papers are member-only). The prior 35/35/35/30 NZA pulse convention is retained as the sensitivity comparator and remains the basis of the CPRS first-decision schedule (documented convention tension - flagged for the team data pass).</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>No public source documents an authoritative cement kiln shell/drive/refractory-system OVERHAUL campaign length distinct from the general kiln retirement-age figure. This is a materially weaker sourcing situation than steel's SPPL, which is grounded in GEM's unit-level blast-furnace relining-history table. CPPL is set equal to the same 35/35/35/30 NZA-derived figures used for CPAL as the best available DRAFT proxy pending a kiln-campaign-specific data source (e.g. PCA Plant Information Summary, member-only).</t>
+          <t>No public source documents an authoritative cement kiln shell/drive/refractory-system OVERHAUL campaign length distinct from the general kiln retirement-age figure. This is a materially weaker sourcing situation than steel's SPPL, which is grounded in GEM's unit-level blast-furnace relining-history table. The 25-yr mean sits in ECRA's 20-30 reinvestment band; pending a kiln-campaign-specific source (e.g. PCA Plant Information Summary, member-only; full ECRA Technology Papers).</t>
         </is>
       </c>
     </row>
@@ -557,12 +557,43 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Provenance</t>
+          <t>Q4 decision-curve change</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Written by Claude Code (Fable/Sonnet agent session), cement industry breakout, worktree cement-industry-breakout-f901fc, 2026-08-26. This is a DRAFT input for staff review, not a finished or approved EI position; verify all figures against primary sources before use in any work product. Reviewed by: (pending).</t>
+          <t>2026-08-26: the overhaul recurrence became a distributed curve (DELAY3) with CPPL as its MEAN, and model-run capacity now joins the decision pool through the same chain (replacing 1/CPAL decay). CPPL moved 35 -&gt; 25 with that change; run the 35-yr value as a sensitivity against the default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Source (chosen value):</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>European Cement Research Academy (ECRA) - reinvestment-cycle commentary</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>'After 20-30 years most of the original equipment has been replaced' - snippet-tier retrieval; full ECRA Technology Papers are member-only, UNCONFIRMED. Basis for the chosen 25-yr MEAN. The NZA 35-yr figure above remains the sensitivity comparator and the CPRS schedule convention. [SNIPPET - verify against the full ECRA source before release]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Anchor tab note</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The 'NZA Anchor' tab now hosts BOTH anchors: B2 = NZA 35 (comparator), B3 = ECRA-informed 25 (chosen mean; the Derivation tab points here).</t>
         </is>
       </c>
     </row>
@@ -580,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,6 +643,21 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>EIA IDM 30-yr assumption extended by 5 - no campaign-specific source exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ECRA reinvestment band (basis for chosen 25-yr mean)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ECRA: most original equipment replaced after 20-30 years; snippet-tier, UNCONFIRMED; chosen mean 25</t>
         </is>
       </c>
     </row>
@@ -632,7 +678,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Chosen campaign length per pathway (see About tab notes)</t>
+          <t>Chosen MEAN campaign length per pathway (see About tab notes; Q4 decision-curve change 2026-08-26)</t>
         </is>
       </c>
     </row>
@@ -660,12 +706,12 @@
         </is>
       </c>
       <c r="B4">
-        <f>'NZA Anchor'!B2</f>
+        <f>'NZA Anchor'!B3</f>
         <v/>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NZA proxy anchor (weakest-sourced parameter class)</t>
+          <t>ECRA-informed 20-30 band, mean 25 (UNCONFIRMED; weakest-sourced parameter class)</t>
         </is>
       </c>
     </row>
@@ -676,7 +722,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>'NZA Anchor'!B2</f>
+        <f>'NZA Anchor'!B3</f>
         <v/>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,12 +738,12 @@
         </is>
       </c>
       <c r="B6">
-        <f>'NZA Anchor'!B2</f>
+        <f>'NZA Anchor'!B3</f>
         <v/>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mirrors the NZA proxy anchor</t>
+          <t>Mirrors the ECRA-informed anchor</t>
         </is>
       </c>
     </row>
@@ -708,11 +754,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EI judgment, matches its shorter CPAL</t>
+          <t>Uniform pending data (previously rode its shorter CPAL at 30)</t>
         </is>
       </c>
     </row>
@@ -864,7 +910,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unit: years between kiln overhaul decisions (DRAFT NZA 35-yr convention; weakest-sourced parameter - verify before release)</t>
+          <t>Unit: mean years between kiln overhaul decisions (25 = ECRA-informed 20-30 band midpoint-high, UNCONFIRMED; weakest-sourced parameter - verify before release)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -880,7 +926,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -890,7 +936,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -900,7 +946,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -910,7 +956,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/indst/CPPL/Cement Pathway Campaign Length.xlsx
+++ b/InputData/indst/CPPL/Cement Pathway Campaign Length.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,6 +594,18 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>The 'NZA Anchor' tab now hosts BOTH anchors: B2 = NZA 35 (comparator), B3 = ECRA-informed 25 (chosen mean; the Derivation tab points here).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Source upgrade (2026-08-27)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Both anchors verified against FULL documents in hand: (1) IEA commentary, Levi/Fernandez Pales/Gul, 20 Jul 2020, 'Aligning investment and innovation in heavy industries to accelerate the transition to net-zero emissions' - 25-year investment cycles for cement kilns ('the story is similar to blast furnaces'), 40-year typical plant lifetimes, 'one or two cycles is most common'; https://www.iea.org/commentaries/aligning-investment-and-innovation-in-heavy-industries-to-accelerate-the-transition-to-net-zero-emissions . (2) ECRA/CSI Technology Papers 2017, p.9 (full 190-page PDF): kiln lifetime 'usually 30 to 50 years'; 'often after 20 or 30 years most of the original equipment has been replaced' - ROLLING piecemeal turnover, which supports the distributed (DELAY3) recurrence form specifically. Neither source gives a discrete kiln-campaign statistic; 25 = the IEA cycle figure. UNCONFIRMED caveat retired; re-verify quotes against the source PDFs before external use.</t>
         </is>
       </c>
     </row>
